--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15380"/>
+    <workbookView windowHeight="22180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>##var</t>
   </si>
@@ -95,115 +95,205 @@
     <t>字段变体</t>
   </si>
   <si>
-    <t>item.ItemExchange</t>
+    <t>test.TestExcelBean1</t>
+  </si>
+  <si>
+    <t>这是个测试excel结构</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>最高品质</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>黑色的</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>蓝色的</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>最差品质</t>
+  </si>
+  <si>
+    <t>test.TestExcelBean2</t>
+  </si>
+  <si>
+    <t>y1</t>
+  </si>
+  <si>
+    <t>y2</t>
+  </si>
+  <si>
+    <t>y3</t>
+  </si>
+  <si>
+    <t>test.Shape</t>
+  </si>
+  <si>
+    <t>test.Circle</t>
+  </si>
+  <si>
+    <t>Shape</t>
+  </si>
+  <si>
+    <t>圆</t>
+  </si>
+  <si>
+    <t>这是一个圆</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>半径</t>
+  </si>
+  <si>
+    <t>test.Rectangle</t>
+  </si>
+  <si>
+    <t>矩形</t>
+  </si>
+  <si>
+    <t>这是一个矩形</t>
+  </si>
+  <si>
+    <t>width</t>
+  </si>
+  <si>
+    <t>宽度</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>高度</t>
+  </si>
+  <si>
+    <t>stacklands.CardRequirement</t>
   </si>
   <si>
     <t>,</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>道具id</t>
-  </si>
-  <si>
-    <t>num</t>
-  </si>
-  <si>
-    <t>道具数量</t>
-  </si>
-  <si>
-    <t>test.TestExcelBean1</t>
-  </si>
-  <si>
-    <t>这是个测试excel结构</t>
-  </si>
-  <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>x2</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>黑色的</t>
-  </si>
-  <si>
-    <t>x3</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>x4</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>test.TestExcelBean2</t>
-  </si>
-  <si>
-    <t>y1</t>
-  </si>
-  <si>
-    <t>y2</t>
-  </si>
-  <si>
-    <t>y3</t>
-  </si>
-  <si>
-    <t>test.Shape</t>
-  </si>
-  <si>
-    <t>test.Circle</t>
-  </si>
-  <si>
-    <t>Shape</t>
-  </si>
-  <si>
-    <t>圆</t>
-  </si>
-  <si>
-    <t>这是一个圆</t>
-  </si>
-  <si>
-    <t>radius</t>
-  </si>
-  <si>
-    <t>半径</t>
-  </si>
-  <si>
-    <t>test.Rectangle</t>
-  </si>
-  <si>
-    <t>矩形</t>
-  </si>
-  <si>
-    <t>这是一个矩形</t>
-  </si>
-  <si>
-    <t>width</t>
-  </si>
-  <si>
-    <t>宽度</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>高度</t>
+    <t>matcher</t>
+  </si>
+  <si>
+    <t>stacklands.ECardMatcher</t>
+  </si>
+  <si>
+    <t>匹配方式</t>
+  </si>
+  <si>
+    <t>card_id</t>
+  </si>
+  <si>
+    <t>string?</t>
+  </si>
+  <si>
+    <t>卡牌 ID</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>标签</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>consume_mode</t>
+  </si>
+  <si>
+    <t>stacklands.EConsumeMode</t>
+  </si>
+  <si>
+    <t>消耗方式</t>
+  </si>
+  <si>
+    <t>stacklands.CardAmount</t>
+  </si>
+  <si>
+    <t>stacklands.QuestCondition</t>
+  </si>
+  <si>
+    <t>metric</t>
+  </si>
+  <si>
+    <t>stacklands.EQuestMetric</t>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>target_id</t>
+  </si>
+  <si>
+    <t>通用目标 ID</t>
+  </si>
+  <si>
+    <t>target_card_id</t>
+  </si>
+  <si>
+    <t>目标卡牌</t>
+  </si>
+  <si>
+    <t>target_pack_id</t>
+  </si>
+  <si>
+    <t>目标卡包</t>
+  </si>
+  <si>
+    <t>target_recipe_id</t>
+  </si>
+  <si>
+    <t>目标配方</t>
+  </si>
+  <si>
+    <t>compare</t>
+  </si>
+  <si>
+    <t>stacklands.ECompareOp</t>
+  </si>
+  <si>
+    <t>比较符</t>
+  </si>
+  <si>
+    <t>threshold</t>
+  </si>
+  <si>
+    <t>阈值</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>stacklands.EQuestPersistence</t>
+  </si>
+  <si>
+    <t>条件统计范围</t>
   </si>
 </sst>
 </file>
@@ -216,25 +306,29 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -242,7 +336,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -250,14 +344,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -265,7 +359,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +367,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -281,7 +375,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -289,7 +383,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -297,14 +391,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -312,7 +406,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -320,7 +414,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -328,14 +422,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -343,33 +437,47 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -378,42 +486,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -563,11 +689,137 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="19">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -670,80 +922,71 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -752,91 +995,117 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="23" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="22" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -886,8 +1155,223 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -897,9 +1381,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="ChatGPT">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -907,160 +1391,100 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="ChatGPT">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1068,26 +1492,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1099,7 +1520,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1117,22 +1538,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1154,331 +1575,845 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5089285714286" customWidth="1"/>
-    <col min="13" max="13" width="10.3839285714286" customWidth="1"/>
+    <col min="1" max="1" width="8.66911764705882" customWidth="1"/>
+    <col min="2" max="2" width="21.6691176470588" customWidth="1"/>
+    <col min="3" max="6" width="8.66911764705882" customWidth="1"/>
+    <col min="7" max="7" width="15.7794117647059" customWidth="1"/>
+    <col min="8" max="9" width="8.66911764705882" customWidth="1"/>
+    <col min="10" max="10" width="12.2205882352941" customWidth="1"/>
+    <col min="11" max="11" width="8.66911764705882" customWidth="1"/>
+    <col min="12" max="12" width="22.6691176470588" customWidth="1"/>
+    <col min="13" max="13" width="8.66911764705882" customWidth="1"/>
+    <col min="14" max="14" width="10.2205882352941" customWidth="1"/>
+    <col min="15" max="16" width="8.66911764705882" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" ht="18" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:16">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
+    <row r="3" ht="18" customHeight="1" spans="1:16">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P3" t="s">
+      <c r="O3" s="3"/>
+      <c r="P3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:16">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="J4" s="2" t="s">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="M4" s="5"/>
+      <c r="N4" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="10:14">
-      <c r="J5" s="2" t="s">
+      <c r="O4" s="5"/>
+      <c r="P4" s="6"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
+      <c r="K5" s="8"/>
+      <c r="L5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="9"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="M6" s="8"/>
+      <c r="N6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="9"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="9"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="8"/>
+      <c r="P8" s="9"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="2:14">
-      <c r="B6" s="2" t="s">
+      <c r="M9" s="8"/>
+      <c r="N9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="O9" s="8"/>
+      <c r="P9" s="9"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L6" t="s">
+      <c r="O10" s="8"/>
+      <c r="P10" s="9"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="9"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="8"/>
+      <c r="P12" s="9"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="7"/>
+      <c r="B13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O13" s="8"/>
+      <c r="P13" s="9"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="8"/>
+      <c r="P14" s="9"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="9"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O16" s="8"/>
+      <c r="P16" s="9"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="O17" s="8"/>
+      <c r="P17" s="9"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="10:14">
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="10:14">
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="M18" s="8"/>
+      <c r="N18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O18" s="8"/>
+      <c r="P18" s="9"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O19" s="8"/>
+      <c r="P19" s="9"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="7"/>
+      <c r="B20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O20" s="8"/>
+      <c r="P20" s="9"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="10:14">
-      <c r="J9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M21" s="8"/>
+      <c r="N21" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O21" s="8"/>
+      <c r="P21" s="9"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="7"/>
+      <c r="B22" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O22" s="8"/>
+      <c r="P22" s="9"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O23" s="8"/>
+      <c r="P23" s="9"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O24" s="8"/>
+      <c r="P24" s="9"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O25" s="8"/>
+      <c r="P25" s="9"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="O26" s="8"/>
+      <c r="P26" s="9"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="O27" s="8"/>
+      <c r="P27" s="9"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="10:14">
-      <c r="J11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="10:14">
-      <c r="J12" t="s">
-        <v>44</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="B13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="2:14">
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14">
-      <c r="B15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="O28" s="8"/>
+      <c r="P28" s="9"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="O29" s="11"/>
+      <c r="P29" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="55">
     <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A29"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B29"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C29"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D22:D29"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E29"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="F15:F19"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="F22:F29"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="G15:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G22:G29"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H29"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>